--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/129.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/129.xlsx
@@ -426,13 +426,13 @@
         <v>-16.92097011118585</v>
       </c>
       <c r="E2">
-        <v>-11.31813037592832</v>
+        <v>-12.30761553202631</v>
       </c>
       <c r="F2">
-        <v>-2.554487237671914</v>
+        <v>-3.334458931697664</v>
       </c>
       <c r="G2">
-        <v>-7.838555013876229</v>
+        <v>-9.210026876406694</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.47509901992373</v>
       </c>
       <c r="E3">
-        <v>-11.11010133696396</v>
+        <v>-11.66322726615685</v>
       </c>
       <c r="F3">
-        <v>-2.230495350721569</v>
+        <v>-3.190051299102432</v>
       </c>
       <c r="G3">
-        <v>-8.127282823778009</v>
+        <v>-9.082430013624567</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.93063290837888</v>
       </c>
       <c r="E4">
-        <v>-11.9015427392845</v>
+        <v>-10.80184358278783</v>
       </c>
       <c r="F4">
-        <v>-1.891395699078966</v>
+        <v>-3.205200482164829</v>
       </c>
       <c r="G4">
-        <v>-8.083553984055289</v>
+        <v>-8.201231714063214</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.32497634545086</v>
       </c>
       <c r="E5">
-        <v>-12.73992630316856</v>
+        <v>-13.28577950310513</v>
       </c>
       <c r="F5">
-        <v>-2.235892164350807</v>
+        <v>-2.591394318936243</v>
       </c>
       <c r="G5">
-        <v>-7.460105481652995</v>
+        <v>-8.327985302904564</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.66413593182217</v>
       </c>
       <c r="E6">
-        <v>-13.70646568146969</v>
+        <v>-12.55058627643386</v>
       </c>
       <c r="F6">
-        <v>-1.688651120508981</v>
+        <v>-2.079096297246708</v>
       </c>
       <c r="G6">
-        <v>-6.149667621349762</v>
+        <v>-7.512463934077054</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.96373091004343</v>
       </c>
       <c r="E7">
-        <v>-14.40843349434669</v>
+        <v>-13.6125406020766</v>
       </c>
       <c r="F7">
-        <v>-1.938419631433685</v>
+        <v>-1.9175041828804</v>
       </c>
       <c r="G7">
-        <v>-6.39768203414195</v>
+        <v>-6.245177418502078</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.22928703406089</v>
       </c>
       <c r="E8">
-        <v>-15.66056108594155</v>
+        <v>-12.79677676586086</v>
       </c>
       <c r="F8">
-        <v>-1.637759540750591</v>
+        <v>-1.643080972946175</v>
       </c>
       <c r="G8">
-        <v>-5.806222160722683</v>
+        <v>-5.76925263741242</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.48785308752124</v>
       </c>
       <c r="E9">
-        <v>-14.95254323179031</v>
+        <v>-15.43549139928633</v>
       </c>
       <c r="F9">
-        <v>-1.82193212214981</v>
+        <v>-2.104482444672902</v>
       </c>
       <c r="G9">
-        <v>-5.642492486127951</v>
+        <v>-4.819742586204987</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.75371230745369</v>
       </c>
       <c r="E10">
-        <v>-15.86782481279862</v>
+        <v>-15.45720543215311</v>
       </c>
       <c r="F10">
-        <v>-1.484001296912558</v>
+        <v>-1.481145086107705</v>
       </c>
       <c r="G10">
-        <v>-4.749130698245736</v>
+        <v>-5.621075953009456</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.03933511994424</v>
       </c>
       <c r="E11">
-        <v>-16.48980166080413</v>
+        <v>-16.65449320351508</v>
       </c>
       <c r="F11">
-        <v>-1.251983042695041</v>
+        <v>-1.270348776382509</v>
       </c>
       <c r="G11">
-        <v>-4.621855395176435</v>
+        <v>-5.226692808893557</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.35213621394642</v>
       </c>
       <c r="E12">
-        <v>-17.73506861427737</v>
+        <v>-17.92616568892705</v>
       </c>
       <c r="F12">
-        <v>-1.065677415233613</v>
+        <v>-1.378656157563739</v>
       </c>
       <c r="G12">
-        <v>-3.765292507083392</v>
+        <v>-3.529782829654248</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.697771470053864</v>
       </c>
       <c r="E13">
-        <v>-18.16365245131131</v>
+        <v>-18.20124784252299</v>
       </c>
       <c r="F13">
-        <v>-1.129398749326562</v>
+        <v>-0.9195384947665297</v>
       </c>
       <c r="G13">
-        <v>-2.690190419466652</v>
+        <v>-3.370331867973031</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.098848376848512</v>
       </c>
       <c r="E14">
-        <v>-18.64931770321193</v>
+        <v>-18.04064551184096</v>
       </c>
       <c r="F14">
-        <v>-0.8035604314353766</v>
+        <v>-1.334309508654867</v>
       </c>
       <c r="G14">
-        <v>-1.976787228012182</v>
+        <v>-2.649198118524509</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.563029439451304</v>
       </c>
       <c r="E15">
-        <v>-19.6776933940878</v>
+        <v>-18.7937669671086</v>
       </c>
       <c r="F15">
-        <v>-1.20065325658057</v>
+        <v>-1.130494679400466</v>
       </c>
       <c r="G15">
-        <v>-1.988701343494526</v>
+        <v>-1.537477598304367</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.09378046099784</v>
       </c>
       <c r="E16">
-        <v>-20.70649023304638</v>
+        <v>-20.04086342408094</v>
       </c>
       <c r="F16">
-        <v>-0.503321979760307</v>
+        <v>-0.9781670260670675</v>
       </c>
       <c r="G16">
-        <v>-1.747502027881304</v>
+        <v>-0.9924240414003269</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.684771779072966</v>
       </c>
       <c r="E17">
-        <v>-21.37099398045792</v>
+        <v>-21.20843534900458</v>
       </c>
       <c r="F17">
-        <v>-0.7772125494545327</v>
+        <v>-0.8830555376124339</v>
       </c>
       <c r="G17">
-        <v>-0.8593212888414521</v>
+        <v>-2.339752675696397</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.331484446642126</v>
       </c>
       <c r="E18">
-        <v>-22.84170648392902</v>
+        <v>-21.77401005324455</v>
       </c>
       <c r="F18">
-        <v>-0.685877587989262</v>
+        <v>-1.113694560104289</v>
       </c>
       <c r="G18">
-        <v>-1.053595854933055</v>
+        <v>-0.2578799394383545</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.034787403601842</v>
       </c>
       <c r="E19">
-        <v>-22.98522741065412</v>
+        <v>-23.0221752300827</v>
       </c>
       <c r="F19">
-        <v>-0.759622996023488</v>
+        <v>-0.1313054926326602</v>
       </c>
       <c r="G19">
-        <v>-0.2262752133777831</v>
+        <v>-0.8104835871506769</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.786772174405615</v>
       </c>
       <c r="E20">
-        <v>-23.92664281516069</v>
+        <v>-23.77127992890554</v>
       </c>
       <c r="F20">
-        <v>-0.4081806700791725</v>
+        <v>-0.6456528952767208</v>
       </c>
       <c r="G20">
-        <v>0.403030269508119</v>
+        <v>0.06292837365011475</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.578990685318213</v>
       </c>
       <c r="E21">
-        <v>-23.4451301739251</v>
+        <v>-24.17243932734903</v>
       </c>
       <c r="F21">
-        <v>-0.1517396597249184</v>
+        <v>-0.5559307651447007</v>
       </c>
       <c r="G21">
-        <v>0.7451271480742656</v>
+        <v>0.418163263340278</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.399427998207665</v>
       </c>
       <c r="E22">
-        <v>-24.98317655741626</v>
+        <v>-24.12898861924543</v>
       </c>
       <c r="F22">
-        <v>-0.3994728719409442</v>
+        <v>-0.8519172069412005</v>
       </c>
       <c r="G22">
-        <v>0.8709094953340193</v>
+        <v>0.998772137062461</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.245467750089871</v>
       </c>
       <c r="E23">
-        <v>-24.62884158021208</v>
+        <v>-24.45708561804916</v>
       </c>
       <c r="F23">
-        <v>-0.141069459209458</v>
+        <v>-0.7743869882435835</v>
       </c>
       <c r="G23">
-        <v>1.082367818732434</v>
+        <v>0.8224458529010209</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.116263798303435</v>
       </c>
       <c r="E24">
-        <v>-26.19707024296436</v>
+        <v>-26.53284300521109</v>
       </c>
       <c r="F24">
-        <v>-0.08505774053436378</v>
+        <v>-0.7109920309073374</v>
       </c>
       <c r="G24">
-        <v>0.9571235918084292</v>
+        <v>1.363374914304839</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.006980614760355</v>
       </c>
       <c r="E25">
-        <v>-26.18351199178539</v>
+        <v>-25.02309505579387</v>
       </c>
       <c r="F25">
-        <v>0.06312476231542577</v>
+        <v>-0.2656989916954492</v>
       </c>
       <c r="G25">
-        <v>0.9775754457884481</v>
+        <v>0.4875414119931771</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.912320759569103</v>
       </c>
       <c r="E26">
-        <v>-25.74433152557351</v>
+        <v>-25.89863022043686</v>
       </c>
       <c r="F26">
-        <v>0.01586143178129718</v>
+        <v>-0.5619836457569567</v>
       </c>
       <c r="G26">
-        <v>1.517897481203769</v>
+        <v>1.292782713674945</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.826282303203911</v>
       </c>
       <c r="E27">
-        <v>-25.85013932076273</v>
+        <v>-25.24063389017434</v>
       </c>
       <c r="F27">
-        <v>-0.1846780327624351</v>
+        <v>-0.4121626321844298</v>
       </c>
       <c r="G27">
-        <v>1.77286808370198</v>
+        <v>1.87598375242909</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.754084627608414</v>
       </c>
       <c r="E28">
-        <v>-25.31949273654391</v>
+        <v>-25.93827701037401</v>
       </c>
       <c r="F28">
-        <v>0.0084574839350752</v>
+        <v>-0.1238932611124102</v>
       </c>
       <c r="G28">
-        <v>1.732597651502915</v>
+        <v>1.480196245485749</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.700312763256546</v>
       </c>
       <c r="E29">
-        <v>-25.86791810971684</v>
+        <v>-25.58530510384615</v>
       </c>
       <c r="F29">
-        <v>-0.2861339871551102</v>
+        <v>-0.1893301440965572</v>
       </c>
       <c r="G29">
-        <v>1.240237231621998</v>
+        <v>1.449835102396207</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.667023218099871</v>
       </c>
       <c r="E30">
-        <v>-26.1085974462765</v>
+        <v>-26.0686246062108</v>
       </c>
       <c r="F30">
-        <v>-0.03183347816968995</v>
+        <v>0.09250281225571023</v>
       </c>
       <c r="G30">
-        <v>1.282204055367296</v>
+        <v>1.160188550457784</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.653065537035429</v>
       </c>
       <c r="E31">
-        <v>-26.24841860973733</v>
+        <v>-24.07197060301485</v>
       </c>
       <c r="F31">
-        <v>0.03837728615679054</v>
+        <v>-0.3550814911923214</v>
       </c>
       <c r="G31">
-        <v>1.163105556424131</v>
+        <v>0.2396877790574016</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.654790257802635</v>
       </c>
       <c r="E32">
-        <v>-24.94331692920074</v>
+        <v>-23.5898330323662</v>
       </c>
       <c r="F32">
-        <v>-0.4135244681946322</v>
+        <v>-0.02736195092937822</v>
       </c>
       <c r="G32">
-        <v>1.141262464502907</v>
+        <v>-0.2947969632036671</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.675311573894215</v>
       </c>
       <c r="E33">
-        <v>-25.68548853431784</v>
+        <v>-24.15245064307917</v>
       </c>
       <c r="F33">
-        <v>-0.4973709883385953</v>
+        <v>0.1208528582491205</v>
       </c>
       <c r="G33">
-        <v>0.5646993369635196</v>
+        <v>-0.2004651245911909</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.712593815527915</v>
       </c>
       <c r="E34">
-        <v>-23.70292714223377</v>
+        <v>-24.19036755594539</v>
       </c>
       <c r="F34">
-        <v>-0.1747840125033978</v>
+        <v>-0.2237902280530166</v>
       </c>
       <c r="G34">
-        <v>0.5513907023184118</v>
+        <v>0.8816489334980819</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.76236616517362</v>
       </c>
       <c r="E35">
-        <v>-22.88753464088665</v>
+        <v>-23.32483126191134</v>
       </c>
       <c r="F35">
-        <v>-0.1472739310564262</v>
+        <v>-0.4521388146761311</v>
       </c>
       <c r="G35">
-        <v>0.9634858804121925</v>
+        <v>-1.426772464110262</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.817162002910463</v>
       </c>
       <c r="E36">
-        <v>-23.26886385165054</v>
+        <v>-22.20402488806491</v>
       </c>
       <c r="F36">
-        <v>-0.551525507296613</v>
+        <v>-0.2032690823834644</v>
       </c>
       <c r="G36">
-        <v>0.4539417032244632</v>
+        <v>-2.536934404089668</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.871894673812897</v>
       </c>
       <c r="E37">
-        <v>-21.87190660434237</v>
+        <v>-20.64032922779432</v>
       </c>
       <c r="F37">
-        <v>-0.2975000162889222</v>
+        <v>-0.03454803814866393</v>
       </c>
       <c r="G37">
-        <v>-0.1656513638454825</v>
+        <v>-1.514390923412114</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.930526682475503</v>
       </c>
       <c r="E38">
-        <v>-21.96096810265122</v>
+        <v>-19.43738539239676</v>
       </c>
       <c r="F38">
-        <v>-0.2479412796816362</v>
+        <v>0.443171443045811</v>
       </c>
       <c r="G38">
-        <v>-0.5865631842694912</v>
+        <v>-1.63815203819125</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.994650518990489</v>
       </c>
       <c r="E39">
-        <v>-20.16610742971108</v>
+        <v>-18.9247168499884</v>
       </c>
       <c r="F39">
-        <v>-0.1592753179881855</v>
+        <v>-0.2519099879084486</v>
       </c>
       <c r="G39">
-        <v>-0.5248762189519305</v>
+        <v>-2.04741552207923</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.067442881672918</v>
       </c>
       <c r="E40">
-        <v>-20.15249936531803</v>
+        <v>-20.54265910039688</v>
       </c>
       <c r="F40">
-        <v>-0.2055305253931071</v>
+        <v>0.0337591378861833</v>
       </c>
       <c r="G40">
-        <v>-0.7527964309140793</v>
+        <v>-2.185591043169006</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.148143905900846</v>
       </c>
       <c r="E41">
-        <v>-20.36269754333206</v>
+        <v>-18.04723896999612</v>
       </c>
       <c r="F41">
-        <v>-0.1536515316905797</v>
+        <v>0.03832261390820577</v>
       </c>
       <c r="G41">
-        <v>-1.414074136675211</v>
+        <v>-2.9604252646594</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.242660985342777</v>
       </c>
       <c r="E42">
-        <v>-18.76091288818295</v>
+        <v>-17.18587792899714</v>
       </c>
       <c r="F42">
-        <v>-0.2122742644192979</v>
+        <v>0.1184597048224327</v>
       </c>
       <c r="G42">
-        <v>-1.4604673283042</v>
+        <v>-1.833102535924098</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.359543799104222</v>
       </c>
       <c r="E43">
-        <v>-18.13685294213391</v>
+        <v>-17.12478428615966</v>
       </c>
       <c r="F43">
-        <v>0.1749717574088178</v>
+        <v>-0.6702388397918101</v>
       </c>
       <c r="G43">
-        <v>-0.9039754330439352</v>
+        <v>-1.832488947492482</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.502595116790636</v>
       </c>
       <c r="E44">
-        <v>-17.48238882159738</v>
+        <v>-16.50866728352008</v>
       </c>
       <c r="F44">
-        <v>0.2417232594612076</v>
+        <v>0.3233671506811269</v>
       </c>
       <c r="G44">
-        <v>-1.955981002103743</v>
+        <v>-3.707775974367885</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.673114365587373</v>
       </c>
       <c r="E45">
-        <v>-17.18976788816973</v>
+        <v>-14.46383484535653</v>
       </c>
       <c r="F45">
-        <v>0.3584965554990483</v>
+        <v>0.4432443393772573</v>
       </c>
       <c r="G45">
-        <v>-2.423807728384693</v>
+        <v>-2.979184008314746</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.864681227152722</v>
       </c>
       <c r="E46">
-        <v>-15.48104331932949</v>
+        <v>-15.19747027696917</v>
       </c>
       <c r="F46">
-        <v>0.1821238815645888</v>
+        <v>0.04061387814434921</v>
       </c>
       <c r="G46">
-        <v>-1.296937808224594</v>
+        <v>-4.07576497225961</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.079538496396117</v>
       </c>
       <c r="E47">
-        <v>-16.23373004109239</v>
+        <v>-13.47199941124856</v>
       </c>
       <c r="F47">
-        <v>0.07127755429377851</v>
+        <v>-0.05694792108776536</v>
       </c>
       <c r="G47">
-        <v>-1.995982374134934</v>
+        <v>-3.365478941286613</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.317933951370986</v>
       </c>
       <c r="E48">
-        <v>-14.68020533344302</v>
+        <v>-12.83412309100212</v>
       </c>
       <c r="F48">
-        <v>0.4388109170374744</v>
+        <v>0.0942456972712004</v>
       </c>
       <c r="G48">
-        <v>-2.615388411575991</v>
+        <v>-3.375371824288338</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.57620641590142</v>
       </c>
       <c r="E49">
-        <v>-14.42756176855509</v>
+        <v>-14.23013388724269</v>
       </c>
       <c r="F49">
-        <v>0.4243567342260258</v>
+        <v>0.05045322615480174</v>
       </c>
       <c r="G49">
-        <v>-2.451445457579895</v>
+        <v>-4.802637578215601</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.847616549784726</v>
       </c>
       <c r="E50">
-        <v>-13.03540470369505</v>
+        <v>-12.41405731357661</v>
       </c>
       <c r="F50">
-        <v>0.4081273600703779</v>
+        <v>0.6364635211824504</v>
       </c>
       <c r="G50">
-        <v>-2.861765494810017</v>
+        <v>-3.879518392010781</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.120702123319784</v>
       </c>
       <c r="E51">
-        <v>-12.78338606822018</v>
+        <v>-10.81636187045642</v>
       </c>
       <c r="F51">
-        <v>0.6323846400910657</v>
+        <v>0.3075453332876563</v>
       </c>
       <c r="G51">
-        <v>-3.153088750965316</v>
+        <v>-3.955009456428926</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.39464252721187</v>
       </c>
       <c r="E52">
-        <v>-12.43435393407898</v>
+        <v>-8.875294885704628</v>
       </c>
       <c r="F52">
-        <v>0.2530520120618936</v>
+        <v>0.02744449317464267</v>
       </c>
       <c r="G52">
-        <v>-3.013807458210006</v>
+        <v>-4.451835618852248</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.666347018954548</v>
       </c>
       <c r="E53">
-        <v>-11.79335296676725</v>
+        <v>-9.065137573054185</v>
       </c>
       <c r="F53">
-        <v>0.5117991972655416</v>
+        <v>-0.09168964996117664</v>
       </c>
       <c r="G53">
-        <v>-3.206566099941146</v>
+        <v>-3.975474435295182</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.93097781443713</v>
       </c>
       <c r="E54">
-        <v>-11.42622957896542</v>
+        <v>-10.1780236458612</v>
       </c>
       <c r="F54">
-        <v>0.4815024878755525</v>
+        <v>0.4859317683783214</v>
       </c>
       <c r="G54">
-        <v>-4.215620478787822</v>
+        <v>-4.024876507094183</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.180877070067988</v>
       </c>
       <c r="E55">
-        <v>-10.06951688016341</v>
+        <v>-8.993152950228257</v>
       </c>
       <c r="F55">
-        <v>0.4986977384228646</v>
+        <v>-0.1621232451190102</v>
       </c>
       <c r="G55">
-        <v>-4.35006525096451</v>
+        <v>-5.288212431911586</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.40779260350309</v>
       </c>
       <c r="E56">
-        <v>-10.23207098314274</v>
+        <v>-8.799515401660273</v>
       </c>
       <c r="F56">
-        <v>0.5366303385318596</v>
+        <v>-0.1974663687268539</v>
       </c>
       <c r="G56">
-        <v>-4.227383658078431</v>
+        <v>-5.875442810740729</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.614760583979043</v>
       </c>
       <c r="E57">
-        <v>-9.28505385628868</v>
+        <v>-7.939354406273326</v>
       </c>
       <c r="F57">
-        <v>0.3273060376814385</v>
+        <v>-0.007181264262376666</v>
       </c>
       <c r="G57">
-        <v>-4.783199621697451</v>
+        <v>-5.356412622024645</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.80157571684193</v>
       </c>
       <c r="E58">
-        <v>-9.179214361781408</v>
+        <v>-5.803617380879802</v>
       </c>
       <c r="F58">
-        <v>0.2998970170576085</v>
+        <v>-0.3623330194364283</v>
       </c>
       <c r="G58">
-        <v>-5.13609500041573</v>
+        <v>-5.000213053196005</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.966868296912185</v>
       </c>
       <c r="E59">
-        <v>-8.928142177374141</v>
+        <v>-7.207919813028417</v>
       </c>
       <c r="F59">
-        <v>0.5475134294698395</v>
+        <v>0.03240144371299491</v>
       </c>
       <c r="G59">
-        <v>-5.265306224205103</v>
+        <v>-7.774610568125771</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.10504505883919</v>
       </c>
       <c r="E60">
-        <v>-8.978204457528937</v>
+        <v>-5.380137134052508</v>
       </c>
       <c r="F60">
-        <v>0.378168624580731</v>
+        <v>0.2303216105290752</v>
       </c>
       <c r="G60">
-        <v>-4.961622606435376</v>
+        <v>-6.148552006019551</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.2121037176381</v>
       </c>
       <c r="E61">
-        <v>-7.902768864765357</v>
+        <v>-5.825892944523532</v>
       </c>
       <c r="F61">
-        <v>0.3280333442610965</v>
+        <v>0.2213479064545481</v>
       </c>
       <c r="G61">
-        <v>-5.53022549047155</v>
+        <v>-6.564016998654881</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.29410521407613</v>
       </c>
       <c r="E62">
-        <v>-8.001340158490319</v>
+        <v>-6.830734155981538</v>
       </c>
       <c r="F62">
-        <v>0.3876070427682285</v>
+        <v>-0.1409228381791625</v>
       </c>
       <c r="G62">
-        <v>-5.568582970501459</v>
+        <v>-5.929100626902328</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.35134102132272</v>
       </c>
       <c r="E63">
-        <v>-8.258439741801794</v>
+        <v>-7.451664926491275</v>
       </c>
       <c r="F63">
-        <v>0.2027237221374069</v>
+        <v>-0.6096255401941647</v>
       </c>
       <c r="G63">
-        <v>-5.375512612722173</v>
+        <v>-6.694120714708423</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.38304424297403</v>
       </c>
       <c r="E64">
-        <v>-7.620074346362528</v>
+        <v>-6.315448155596743</v>
       </c>
       <c r="F64">
-        <v>0.2924972110484005</v>
+        <v>-0.8608453508085736</v>
       </c>
       <c r="G64">
-        <v>-6.043976193698488</v>
+        <v>-6.797695754453855</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.38280109146738</v>
       </c>
       <c r="E65">
-        <v>-7.424240487900823</v>
+        <v>-6.290446450600395</v>
       </c>
       <c r="F65">
-        <v>0.2324786792459651</v>
+        <v>-0.623138697636033</v>
       </c>
       <c r="G65">
-        <v>-5.715578415143023</v>
+        <v>-5.326166321689684</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.35002801203465</v>
       </c>
       <c r="E66">
-        <v>-8.279216380548986</v>
+        <v>-7.920914460114092</v>
       </c>
       <c r="F66">
-        <v>0.08589658221838418</v>
+        <v>-0.00787874961553385</v>
       </c>
       <c r="G66">
-        <v>-5.536013565302411</v>
+        <v>-7.223257065827597</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.29161638843346</v>
       </c>
       <c r="E67">
-        <v>-7.260939186710222</v>
+        <v>-6.399460405387044</v>
       </c>
       <c r="F67">
-        <v>0.2013328932681065</v>
+        <v>-0.7983408884303369</v>
       </c>
       <c r="G67">
-        <v>-5.977731611634859</v>
+        <v>-6.914750052365486</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.20833029685544</v>
       </c>
       <c r="E68">
-        <v>-7.785313834428411</v>
+        <v>-5.205052743493949</v>
       </c>
       <c r="F68">
-        <v>0.0001199660258981762</v>
+        <v>-0.7874130656526058</v>
       </c>
       <c r="G68">
-        <v>-5.58104833120579</v>
+        <v>-6.291301549963193</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.09999622971154</v>
       </c>
       <c r="E69">
-        <v>-7.771067255200281</v>
+        <v>-5.707577504125129</v>
       </c>
       <c r="F69">
-        <v>-0.09926755496198651</v>
+        <v>-0.8000025934403527</v>
       </c>
       <c r="G69">
-        <v>-5.901541647024552</v>
+        <v>-7.497675468508637</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.960480969684246</v>
       </c>
       <c r="E70">
-        <v>-7.41843498422299</v>
+        <v>-4.882942387328357</v>
       </c>
       <c r="F70">
-        <v>-0.1850632236047369</v>
+        <v>-0.396399628876558</v>
       </c>
       <c r="G70">
-        <v>-6.047854597581751</v>
+        <v>-5.315774693010922</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.793162151673199</v>
       </c>
       <c r="E71">
-        <v>-8.280217173304681</v>
+        <v>-5.435511314218301</v>
       </c>
       <c r="F71">
-        <v>-0.2602127143867081</v>
+        <v>-0.9300355664948051</v>
       </c>
       <c r="G71">
-        <v>-5.298449843177054</v>
+        <v>-6.175047870112066</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.603720759416539</v>
       </c>
       <c r="E72">
-        <v>-8.008132869501823</v>
+        <v>-7.110236100208961</v>
       </c>
       <c r="F72">
-        <v>0.1123248158372996</v>
+        <v>-0.4010649940891248</v>
       </c>
       <c r="G72">
-        <v>-5.662432469544697</v>
+        <v>-6.587408827152163</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.392796743105105</v>
       </c>
       <c r="E73">
-        <v>-8.126067918083583</v>
+        <v>-6.498502660408803</v>
       </c>
       <c r="F73">
-        <v>0.05013181960251552</v>
+        <v>-1.021725897575877</v>
       </c>
       <c r="G73">
-        <v>-5.360271338578552</v>
+        <v>-5.05501929690341</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.159729587591384</v>
       </c>
       <c r="E74">
-        <v>-7.839999686545038</v>
+        <v>-7.474968453734746</v>
       </c>
       <c r="F74">
-        <v>-0.2726721884922154</v>
+        <v>-0.7630880568693983</v>
       </c>
       <c r="G74">
-        <v>-5.381399124199817</v>
+        <v>-5.330454878267878</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.900156554760651</v>
       </c>
       <c r="E75">
-        <v>-9.223086217967719</v>
+        <v>-7.516797968143598</v>
       </c>
       <c r="F75">
-        <v>-0.569258368288342</v>
+        <v>-0.5809863939771774</v>
       </c>
       <c r="G75">
-        <v>-4.912345221055635</v>
+        <v>-4.052330487882056</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.619578932461806</v>
       </c>
       <c r="E76">
-        <v>-8.911984582114773</v>
+        <v>-6.914728291875808</v>
       </c>
       <c r="F76">
-        <v>-0.3013676636925931</v>
+        <v>0.1376877689762149</v>
       </c>
       <c r="G76">
-        <v>-4.714234906961042</v>
+        <v>-3.556393536501344</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.323384395338794</v>
       </c>
       <c r="E77">
-        <v>-9.937145056445196</v>
+        <v>-7.82992836035198</v>
       </c>
       <c r="F77">
-        <v>-0.09548522940080396</v>
+        <v>-0.7599568280868162</v>
       </c>
       <c r="G77">
-        <v>-3.819675473209629</v>
+        <v>-4.601918692981249</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.013478617387586</v>
       </c>
       <c r="E78">
-        <v>-10.5921797647067</v>
+        <v>-9.141401603817361</v>
       </c>
       <c r="F78">
-        <v>-0.3294426917082739</v>
+        <v>-0.9822367951170216</v>
       </c>
       <c r="G78">
-        <v>-4.25552013295067</v>
+        <v>-4.323999226896281</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.690558275739427</v>
       </c>
       <c r="E79">
-        <v>-11.59948446602488</v>
+        <v>-9.76963680290147</v>
       </c>
       <c r="F79">
-        <v>-0.1697193742026817</v>
+        <v>-0.5755141989142839</v>
       </c>
       <c r="G79">
-        <v>-3.315112190349136</v>
+        <v>-3.031293087900287</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.353119686710114</v>
       </c>
       <c r="E80">
-        <v>-11.99152804629092</v>
+        <v>-9.928658696154823</v>
       </c>
       <c r="F80">
-        <v>-0.3872784754043326</v>
+        <v>-0.4173622943718023</v>
       </c>
       <c r="G80">
-        <v>-3.055075381763142</v>
+        <v>-4.100968035057705</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.009911747309128</v>
       </c>
       <c r="E81">
-        <v>-13.17359561651312</v>
+        <v>-10.36467375903535</v>
       </c>
       <c r="F81">
-        <v>-0.2846189031753899</v>
+        <v>-0.6163775628943835</v>
       </c>
       <c r="G81">
-        <v>-2.771459715050979</v>
+        <v>-2.500270034384433</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.666940557185224</v>
       </c>
       <c r="E82">
-        <v>-13.61877178231116</v>
+        <v>-10.68667090335075</v>
       </c>
       <c r="F82">
-        <v>-0.2365280336058646</v>
+        <v>-0.5919879414537577</v>
       </c>
       <c r="G82">
-        <v>-2.088962349464919</v>
+        <v>-2.229749722916013</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.328053432460785</v>
       </c>
       <c r="E83">
-        <v>-14.34462729557862</v>
+        <v>-12.56476945702588</v>
       </c>
       <c r="F83">
-        <v>-0.4498724014620716</v>
+        <v>-0.7852510267312991</v>
       </c>
       <c r="G83">
-        <v>-1.94270517967423</v>
+        <v>-2.517814726062784</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.996013129717912</v>
       </c>
       <c r="E84">
-        <v>-15.27895563826319</v>
+        <v>-14.66445077237034</v>
       </c>
       <c r="F84">
-        <v>-0.4144249035614752</v>
+        <v>-0.5354352988646354</v>
       </c>
       <c r="G84">
-        <v>-1.691698292819828</v>
+        <v>-0.9072369672740233</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.672495840545501</v>
       </c>
       <c r="E85">
-        <v>-16.67560494933884</v>
+        <v>-15.75718513584322</v>
       </c>
       <c r="F85">
-        <v>-0.2280422379315865</v>
+        <v>-0.5042911696215824</v>
       </c>
       <c r="G85">
-        <v>-0.6025722642580219</v>
+        <v>-1.143504606883399</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.369184058664572</v>
       </c>
       <c r="E86">
-        <v>-18.34663902901325</v>
+        <v>-17.14428389523669</v>
       </c>
       <c r="F86">
-        <v>-0.2832893734938967</v>
+        <v>-0.3276211117895178</v>
       </c>
       <c r="G86">
-        <v>-1.234830846547424</v>
+        <v>-0.07171327182013972</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.09230647496114</v>
       </c>
       <c r="E87">
-        <v>-18.54571074639044</v>
+        <v>-17.81174020770123</v>
       </c>
       <c r="F87">
-        <v>-0.1676376869194465</v>
+        <v>-1.164828023144297</v>
       </c>
       <c r="G87">
-        <v>-0.9004317137597349</v>
+        <v>-0.6929174186757727</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.84622422687383</v>
       </c>
       <c r="E88">
-        <v>-20.83258559178996</v>
+        <v>-20.08788256970258</v>
       </c>
       <c r="F88">
-        <v>-0.3746839774121689</v>
+        <v>-0.7017838988578181</v>
       </c>
       <c r="G88">
-        <v>-0.5158397347772198</v>
+        <v>-0.1635612257121162</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.631773090976526</v>
       </c>
       <c r="E89">
-        <v>-21.79129071005782</v>
+        <v>-20.61526865263587</v>
       </c>
       <c r="F89">
-        <v>-0.06883913515495227</v>
+        <v>-0.1349826155336872</v>
       </c>
       <c r="G89">
-        <v>0.03814858843318826</v>
+        <v>-0.4518952890267611</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.44958092959117</v>
       </c>
       <c r="E90">
-        <v>-23.36454145048461</v>
+        <v>-21.49689461481917</v>
       </c>
       <c r="F90">
-        <v>-0.2000384495125464</v>
+        <v>-0.7567626433816212</v>
       </c>
       <c r="G90">
-        <v>0.9313824086745854</v>
+        <v>0.4180582642503758</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.306324799036497</v>
       </c>
       <c r="E91">
-        <v>-25.80244996098795</v>
+        <v>-24.4039122762511</v>
       </c>
       <c r="F91">
-        <v>-0.2916368318119073</v>
+        <v>-0.6395635664987417</v>
       </c>
       <c r="G91">
-        <v>0.7095947998070388</v>
+        <v>0.006025429366224494</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.201573932027024</v>
       </c>
       <c r="E92">
-        <v>-26.78156038313437</v>
+        <v>-27.20024497598754</v>
       </c>
       <c r="F92">
-        <v>-0.6875417781014862</v>
+        <v>-1.055932501107079</v>
       </c>
       <c r="G92">
-        <v>0.142977054814328</v>
+        <v>0.7115930637367406</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.133167349923949</v>
       </c>
       <c r="E93">
-        <v>-29.41870363607918</v>
+        <v>-28.2245993819446</v>
       </c>
       <c r="F93">
-        <v>-0.7569150629837365</v>
+        <v>-0.868470472751343</v>
       </c>
       <c r="G93">
-        <v>0.5879205419397098</v>
+        <v>0.4790988289207258</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.094302431309249</v>
       </c>
       <c r="E94">
-        <v>-31.29251825334306</v>
+        <v>-29.05352296362664</v>
       </c>
       <c r="F94">
-        <v>-0.5105585973911635</v>
+        <v>-0.9031012003927792</v>
       </c>
       <c r="G94">
-        <v>0.4865111084235114</v>
+        <v>-0.9099177252880896</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.081780986797305</v>
       </c>
       <c r="E95">
-        <v>-33.00236361950021</v>
+        <v>-32.54405261484292</v>
       </c>
       <c r="F95">
-        <v>-0.8103588427101521</v>
+        <v>-1.555242550288121</v>
       </c>
       <c r="G95">
-        <v>0.833684036742119</v>
+        <v>1.080366273581173</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.095142318967087</v>
       </c>
       <c r="E96">
-        <v>-35.99888430545673</v>
+        <v>-32.69831961038822</v>
       </c>
       <c r="F96">
-        <v>-0.9062672206062788</v>
+        <v>-1.563180795109148</v>
       </c>
       <c r="G96">
-        <v>0.6469365929078825</v>
+        <v>-0.2980716223199928</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.127523915356629</v>
       </c>
       <c r="E97">
-        <v>-37.28352860466367</v>
+        <v>-36.20125954462252</v>
       </c>
       <c r="F97">
-        <v>-1.148019620174092</v>
+        <v>-1.488649266409666</v>
       </c>
       <c r="G97">
-        <v>0.6162768586564311</v>
+        <v>-0.04527975093725308</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.176455369125086</v>
       </c>
       <c r="E98">
-        <v>-39.57658708132067</v>
+        <v>-37.70855758960159</v>
       </c>
       <c r="F98">
-        <v>-1.315146885525907</v>
+        <v>-1.534588037466718</v>
       </c>
       <c r="G98">
-        <v>-0.1563162885088623</v>
+        <v>-1.313176573722286</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.229549956173663</v>
       </c>
       <c r="E99">
-        <v>-41.08931476663493</v>
+        <v>-40.48447819274846</v>
       </c>
       <c r="F99">
-        <v>-1.627134900442284</v>
+        <v>-2.218549464405797</v>
       </c>
       <c r="G99">
-        <v>-0.07037125220232682</v>
+        <v>-0.3332922545390725</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.293064506960171</v>
       </c>
       <c r="E100">
-        <v>-44.46190031232144</v>
+        <v>-43.30380648349585</v>
       </c>
       <c r="F100">
-        <v>-1.71441169000124</v>
+        <v>-2.073990240575852</v>
       </c>
       <c r="G100">
-        <v>-0.4692693571840209</v>
+        <v>-2.542246701794409</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.35343391450229</v>
       </c>
       <c r="E101">
-        <v>-46.38249859455856</v>
+        <v>-43.98461500157201</v>
       </c>
       <c r="F101">
-        <v>-2.03063763255034</v>
+        <v>-2.725728175546031</v>
       </c>
       <c r="G101">
-        <v>-0.5749968782724485</v>
+        <v>-1.882734293232259</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.429429539595778</v>
       </c>
       <c r="E102">
-        <v>-48.12605618546581</v>
+        <v>-46.81936048207852</v>
       </c>
       <c r="F102">
-        <v>-2.256409996550748</v>
+        <v>-3.02620022682869</v>
       </c>
       <c r="G102">
-        <v>-1.382085507692184</v>
+        <v>-1.784901391215855</v>
       </c>
     </row>
   </sheetData>
